--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98786</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,7 +784,7 @@
         <v>129914823</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129914825</v>
+        <v>129914823</v>
       </c>
       <c r="B2" t="n">
-        <v>5362</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101728</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695644</v>
+        <v>695705</v>
       </c>
       <c r="R2" t="n">
-        <v>6625093</v>
+        <v>6625086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,6 +764,11 @@
           <t>2025-11-30</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,128 +786,10 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>129914823</v>
-      </c>
-      <c r="B3" t="n">
-        <v>98920</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Gammalbyberg, Upl</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>695705</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6625086</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Skederid</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52133-2022 artfynd.xlsx
+++ b/artfynd/A 52133-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,8 +795,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129914823</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>